--- a/DesignData/Excel_Masters/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>LevelUpCostId</t>
   </si>
@@ -54,16 +51,115 @@
     <t>BaseMoveSpeed</t>
   </si>
   <si>
+    <t>Char_Anubis</t>
+  </si>
+  <si>
+    <t>Char_Army</t>
+  </si>
+  <si>
+    <t>Char_Bard</t>
+  </si>
+  <si>
+    <t>Char_Binder</t>
+  </si>
+  <si>
+    <t>Char_Courier</t>
+  </si>
+  <si>
+    <t>Char_Demonia</t>
+  </si>
+  <si>
+    <t>Char_Enchanter</t>
+  </si>
+  <si>
+    <t>Char_Guard</t>
+  </si>
+  <si>
+    <t>Char_Hermit</t>
+  </si>
+  <si>
+    <t>Char_Hornet</t>
+  </si>
+  <si>
+    <t>Char_Looter</t>
+  </si>
+  <si>
+    <t>Char_Maid</t>
+  </si>
+  <si>
+    <t>Char_Merry</t>
+  </si>
+  <si>
+    <t>Char_Muzzle</t>
+  </si>
+  <si>
+    <t>Char_Noble</t>
+  </si>
+  <si>
+    <t>Char_Nurse</t>
+  </si>
+  <si>
+    <t>Char_Outsider</t>
+  </si>
+  <si>
+    <t>Char_Pioneer</t>
+  </si>
+  <si>
+    <t>Char_Rogue</t>
+  </si>
+  <si>
+    <t>Char_Tinker</t>
+  </si>
+  <si>
+    <t>Char_Tuner</t>
+  </si>
+  <si>
+    <t>Char_Weaver</t>
+  </si>
+  <si>
+    <t>Char_Writer</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>GrowthHPPerLevel</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>BaseCritRate</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TestChar</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cost_Epic</t>
+  </si>
+  <si>
+    <t>Cost_Rare</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t>Cost_Legendary</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Cost_Common</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>Cost_Uncommon</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Rare</t>
   </si>
 </sst>
 </file>
@@ -981,77 +1077,1063 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2">
+        <v>148.5</v>
+      </c>
+      <c r="E2">
+        <v>14.2</v>
+      </c>
+      <c r="F2">
+        <v>7.4</v>
+      </c>
+      <c r="G2">
+        <v>22</v>
+      </c>
+      <c r="H2">
+        <v>3.5</v>
+      </c>
+      <c r="I2">
+        <v>1485</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
+      </c>
+      <c r="K2">
+        <v>141.80000000000001</v>
+      </c>
+      <c r="L2">
+        <v>74.2</v>
+      </c>
+      <c r="M2">
+        <v>600</v>
+      </c>
+      <c r="N2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I3">
+        <v>800</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>80</v>
+      </c>
+      <c r="L3">
+        <v>40</v>
+      </c>
+      <c r="M3">
+        <v>600</v>
+      </c>
+      <c r="N3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>81</v>
+      </c>
+      <c r="E4">
+        <v>8.1</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>1.4</v>
+      </c>
+      <c r="I4">
+        <v>810</v>
+      </c>
+      <c r="J4">
+        <v>150</v>
+      </c>
+      <c r="K4">
+        <v>81</v>
+      </c>
+      <c r="L4">
+        <v>40.5</v>
+      </c>
+      <c r="M4">
+        <v>600</v>
+      </c>
+      <c r="N4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>97.8</v>
+      </c>
+      <c r="E5">
+        <v>12.7</v>
+      </c>
+      <c r="F5">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G5">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>3.8</v>
+      </c>
+      <c r="I5">
+        <v>977.5</v>
+      </c>
+      <c r="J5">
+        <v>150</v>
+      </c>
+      <c r="K5">
+        <v>126.5</v>
+      </c>
+      <c r="L5">
+        <v>46</v>
+      </c>
+      <c r="M5">
+        <v>580</v>
+      </c>
+      <c r="N5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>2.5</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>600</v>
+      </c>
+      <c r="N6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>114.8</v>
+      </c>
+      <c r="E7">
+        <v>15.5</v>
+      </c>
+      <c r="F7">
+        <v>5.4</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>4.7</v>
+      </c>
+      <c r="I7">
+        <v>1147.5</v>
+      </c>
+      <c r="J7">
+        <v>100</v>
+      </c>
+      <c r="K7">
+        <v>155.19999999999999</v>
+      </c>
+      <c r="L7">
+        <v>54</v>
+      </c>
+      <c r="M7">
+        <v>630</v>
+      </c>
+      <c r="N7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8">
+        <v>90</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>4.5</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>1.5</v>
+      </c>
+      <c r="I8">
+        <v>900</v>
+      </c>
+      <c r="J8">
+        <v>150</v>
+      </c>
+      <c r="K8">
+        <v>90</v>
+      </c>
+      <c r="L8">
+        <v>45</v>
+      </c>
+      <c r="M8">
+        <v>600</v>
+      </c>
+      <c r="N8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>6.8</v>
+      </c>
+      <c r="F9">
+        <v>5.2</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>1.8</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <v>68</v>
+      </c>
+      <c r="L9">
+        <v>52</v>
+      </c>
+      <c r="M9">
+        <v>550</v>
+      </c>
+      <c r="N9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>97.8</v>
+      </c>
+      <c r="E10">
+        <v>12.7</v>
+      </c>
+      <c r="F10">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G10">
+        <v>24</v>
+      </c>
+      <c r="H10">
+        <v>3.8</v>
+      </c>
+      <c r="I10">
+        <v>977.5</v>
+      </c>
+      <c r="J10">
+        <v>150</v>
+      </c>
+      <c r="K10">
+        <v>126.5</v>
+      </c>
+      <c r="L10">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>580</v>
+      </c>
+      <c r="N10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11">
+        <v>68</v>
+      </c>
+      <c r="E11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F11">
+        <v>3.2</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>3.6</v>
+      </c>
+      <c r="I11">
+        <v>680</v>
+      </c>
+      <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
+        <v>92</v>
+      </c>
+      <c r="L11">
+        <v>32</v>
+      </c>
+      <c r="M11">
+        <v>630</v>
+      </c>
+      <c r="N11">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12">
+        <v>90</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>4.5</v>
+      </c>
+      <c r="G12">
+        <v>18</v>
+      </c>
+      <c r="H12">
+        <v>2.4</v>
+      </c>
+      <c r="I12">
+        <v>900</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
+        <v>90</v>
+      </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>600</v>
+      </c>
+      <c r="N12">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>97.8</v>
+      </c>
+      <c r="E13">
+        <v>13.2</v>
+      </c>
+      <c r="F13">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>4.3</v>
+      </c>
+      <c r="I13">
+        <v>977.5</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>132.19999999999999</v>
+      </c>
+      <c r="L13">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <v>630</v>
+      </c>
+      <c r="N13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14">
+        <v>81</v>
+      </c>
+      <c r="E14">
+        <v>8.1</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="H14">
+        <v>1.4</v>
+      </c>
+      <c r="I14">
+        <v>810</v>
+      </c>
+      <c r="J14">
+        <v>150</v>
+      </c>
+      <c r="K14">
+        <v>81</v>
+      </c>
+      <c r="L14">
+        <v>40.5</v>
+      </c>
+      <c r="M14">
+        <v>600</v>
+      </c>
+      <c r="N14">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15">
+        <v>90</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15">
+        <v>4.5</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>2.4</v>
+      </c>
+      <c r="I15">
+        <v>900</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>90</v>
+      </c>
+      <c r="L15">
+        <v>45</v>
+      </c>
+      <c r="M15">
+        <v>600</v>
+      </c>
+      <c r="N15">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16">
+        <v>168.8</v>
+      </c>
+      <c r="E16">
+        <v>11.5</v>
+      </c>
+      <c r="F16">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G16">
+        <v>25</v>
+      </c>
+      <c r="H16">
+        <v>2.4</v>
+      </c>
+      <c r="I16">
+        <v>1687.5</v>
+      </c>
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
+        <v>114.8</v>
+      </c>
+      <c r="L16">
+        <v>87.8</v>
+      </c>
+      <c r="M16">
+        <v>550</v>
+      </c>
+      <c r="N16">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>81</v>
+      </c>
+      <c r="E17">
+        <v>7.7</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>25</v>
+      </c>
+      <c r="H17">
+        <v>0.9</v>
+      </c>
+      <c r="I17">
+        <v>810</v>
+      </c>
+      <c r="J17">
+        <v>150</v>
+      </c>
+      <c r="K17">
+        <v>76.5</v>
+      </c>
+      <c r="L17">
+        <v>40.5</v>
+      </c>
+      <c r="M17">
+        <v>600</v>
+      </c>
+      <c r="N17">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18">
+        <v>126.5</v>
+      </c>
+      <c r="E18">
+        <v>12.1</v>
+      </c>
+      <c r="F18">
+        <v>6.3</v>
+      </c>
+      <c r="G18">
+        <v>22</v>
+      </c>
+      <c r="H18">
+        <v>3.2</v>
+      </c>
+      <c r="I18">
+        <v>1265</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>120.7</v>
+      </c>
+      <c r="L18">
+        <v>63.2</v>
+      </c>
+      <c r="M18">
+        <v>600</v>
+      </c>
+      <c r="N18">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19">
+        <v>125</v>
+      </c>
+      <c r="E19">
+        <v>8.5</v>
+      </c>
+      <c r="F19">
+        <v>6.5</v>
+      </c>
+      <c r="G19">
+        <v>25</v>
+      </c>
+      <c r="H19">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I19">
+        <v>1250</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>85</v>
+      </c>
+      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>550</v>
+      </c>
+      <c r="N19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>68</v>
+      </c>
+      <c r="E20">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F20">
+        <v>3.2</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+      <c r="H20">
+        <v>3.6</v>
+      </c>
+      <c r="I20">
+        <v>680</v>
+      </c>
+      <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
+        <v>92</v>
+      </c>
+      <c r="L20">
+        <v>32</v>
+      </c>
+      <c r="M20">
+        <v>630</v>
+      </c>
+      <c r="N20">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>109.2</v>
+      </c>
+      <c r="E21">
+        <v>10.9</v>
+      </c>
+      <c r="F21">
+        <v>5.8</v>
+      </c>
+      <c r="G21">
+        <v>22</v>
+      </c>
+      <c r="H21">
+        <v>2.7</v>
+      </c>
+      <c r="I21">
+        <v>1092.5</v>
+      </c>
+      <c r="J21">
+        <v>120</v>
+      </c>
+      <c r="K21">
+        <v>109.2</v>
+      </c>
+      <c r="L21">
+        <v>57.5</v>
+      </c>
+      <c r="M21">
+        <v>590</v>
+      </c>
+      <c r="N21">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <v>90</v>
+      </c>
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22">
+        <v>4.5</v>
+      </c>
+      <c r="G22">
+        <v>20</v>
+      </c>
+      <c r="H22">
+        <v>1.5</v>
+      </c>
+      <c r="I22">
+        <v>900</v>
+      </c>
+      <c r="J22">
+        <v>150</v>
+      </c>
+      <c r="K22">
+        <v>90</v>
+      </c>
+      <c r="L22">
+        <v>45</v>
+      </c>
+      <c r="M22">
+        <v>600</v>
+      </c>
+      <c r="N22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23">
+        <v>85</v>
+      </c>
+      <c r="E23">
+        <v>11</v>
+      </c>
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>10</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-      <c r="L2">
-        <v>300</v>
-      </c>
-      <c r="M2">
-        <v>0.5</v>
+      <c r="G23">
+        <v>24</v>
+      </c>
+      <c r="H23">
+        <v>3.5</v>
+      </c>
+      <c r="I23">
+        <v>850</v>
+      </c>
+      <c r="J23">
+        <v>150</v>
+      </c>
+      <c r="K23">
+        <v>110</v>
+      </c>
+      <c r="L23">
+        <v>40</v>
+      </c>
+      <c r="M23">
+        <v>580</v>
+      </c>
+      <c r="N23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24">
+        <v>85</v>
+      </c>
+      <c r="E24">
+        <v>11</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+      <c r="G24">
+        <v>24</v>
+      </c>
+      <c r="H24">
+        <v>3.5</v>
+      </c>
+      <c r="I24">
+        <v>850</v>
+      </c>
+      <c r="J24">
+        <v>150</v>
+      </c>
+      <c r="K24">
+        <v>110</v>
+      </c>
+      <c r="L24">
+        <v>40</v>
+      </c>
+      <c r="M24">
+        <v>580</v>
+      </c>
+      <c r="N24">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -1078,5 +2160,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterStats_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>---</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>C_Writer_Ult</t>
+  </si>
+  <si>
+    <t>SummonCost</t>
   </si>
 </sst>
 </file>
@@ -1125,10 +1128,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="15" max="15" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1165,8 +1171,11 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1203,8 +1212,11 @@
       <c r="L2">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1241,8 +1253,11 @@
       <c r="L3">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1279,8 +1294,11 @@
       <c r="L4">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1317,8 +1335,11 @@
       <c r="L5">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1355,8 +1376,11 @@
       <c r="L6">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1393,8 +1417,11 @@
       <c r="L7">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1431,8 +1458,11 @@
       <c r="L8">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1469,8 +1499,11 @@
       <c r="L9">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1507,8 +1540,11 @@
       <c r="L10">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1545,8 +1581,11 @@
       <c r="L11">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1583,8 +1622,11 @@
       <c r="L12">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1621,8 +1663,11 @@
       <c r="L13">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1659,8 +1704,11 @@
       <c r="L14">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1697,8 +1745,11 @@
       <c r="L15">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1735,8 +1786,11 @@
       <c r="L16">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1773,8 +1827,11 @@
       <c r="L17">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1811,8 +1868,11 @@
       <c r="L18">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1849,8 +1909,11 @@
       <c r="L19">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1887,8 +1950,11 @@
       <c r="L20">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1925,8 +1991,11 @@
       <c r="L21">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1963,8 +2032,11 @@
       <c r="L22">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2001,8 +2073,11 @@
       <c r="L23">
         <v>0.05</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -2038,10 +2113,14 @@
       </c>
       <c r="L24">
         <v>0.05</v>
+      </c>
+      <c r="M24">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterStats_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25680" windowHeight="10965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterStats" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,10 @@
     <t>GrowthDefensePerLevel</t>
   </si>
   <si>
-    <t>SkillActionID</t>
+    <t>UltimateActionHandle</t>
+  </si>
+  <si>
+    <t>SummonCost</t>
   </si>
   <si>
     <t>BaseMaxHP</t>
@@ -63,7 +66,7 @@
     <t>Cost_Legendary</t>
   </si>
   <si>
-    <t>C_Anubis_Ult</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Anubis_Ult")</t>
   </si>
   <si>
     <t>Char_Army</t>
@@ -72,145 +75,142 @@
     <t>Cost_Common</t>
   </si>
   <si>
-    <t>C_Army_Ult</t>
-  </si>
-  <si>
     <t>Char_Bard</t>
   </si>
   <si>
     <t>Cost_Uncommon</t>
   </si>
   <si>
-    <t>C_Bard_Ult</t>
-  </si>
-  <si>
     <t>Char_Binder</t>
   </si>
   <si>
     <t>Cost_Epic</t>
   </si>
   <si>
-    <t>C_Binder_Ult</t>
-  </si>
-  <si>
     <t>Char_Courier</t>
   </si>
   <si>
     <t>Cost_Rare</t>
   </si>
   <si>
-    <t>C_Courier_Ult</t>
-  </si>
-  <si>
     <t>Char_Demonia</t>
   </si>
   <si>
-    <t>C_Demonia_Ult</t>
-  </si>
-  <si>
     <t>Char_Enchanter</t>
   </si>
   <si>
-    <t>C_Enchanter_Ult</t>
-  </si>
-  <si>
     <t>Char_Guard</t>
   </si>
   <si>
-    <t>C_Guard_Ult</t>
-  </si>
-  <si>
     <t>Char_Hermit</t>
   </si>
   <si>
-    <t>C_Hermit_Ult</t>
-  </si>
-  <si>
     <t>Char_Hornet</t>
   </si>
   <si>
-    <t>C_Hornet_Ult</t>
-  </si>
-  <si>
     <t>Char_Looter</t>
   </si>
   <si>
-    <t>C_Looter_Ult</t>
-  </si>
-  <si>
     <t>Char_Maid</t>
   </si>
   <si>
-    <t>C_Maid_Ult</t>
-  </si>
-  <si>
     <t>Char_Merry</t>
   </si>
   <si>
-    <t>C_Merry_Ult</t>
-  </si>
-  <si>
     <t>Char_Muzzle</t>
   </si>
   <si>
-    <t>C_Muzzle_Ult</t>
-  </si>
-  <si>
     <t>Char_Noble</t>
   </si>
   <si>
-    <t>C_Noble_Ult</t>
-  </si>
-  <si>
     <t>Char_Nurse</t>
   </si>
   <si>
-    <t>C_Nurse_Ult</t>
-  </si>
-  <si>
     <t>Char_Outsider</t>
   </si>
   <si>
-    <t>C_Outsider_Ult</t>
-  </si>
-  <si>
     <t>Char_Pioneer</t>
   </si>
   <si>
-    <t>C_Pioneer_Ult</t>
-  </si>
-  <si>
     <t>Char_Rogue</t>
   </si>
   <si>
-    <t>C_Rogue_Ult</t>
-  </si>
-  <si>
     <t>Char_Tinker</t>
   </si>
   <si>
-    <t>C_Tinker_Ult</t>
-  </si>
-  <si>
     <t>Char_Tuner</t>
   </si>
   <si>
-    <t>C_Tuner_Ult</t>
-  </si>
-  <si>
     <t>Char_Weaver</t>
   </si>
   <si>
-    <t>C_Weaver_Ult</t>
-  </si>
-  <si>
     <t>Char_Writer</t>
   </si>
   <si>
-    <t>C_Writer_Ult</t>
-  </si>
-  <si>
-    <t>SummonCost</t>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Army_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Bard_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Binder_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Courier_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Demonia_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Enchanter_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Guard_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hermit_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hornet_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Looter_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Maid_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Merry_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Muzzle_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Noble_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Nurse_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Outsider_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Pioneer_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Rogue_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tinker_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tuner_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Weaver_Ult")</t>
+  </si>
+  <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Writer_Ult")</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1131,8 @@
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="15" max="15" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="6" max="6" width="51.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1172,15 +1173,15 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>148.5</v>
@@ -1192,36 +1193,36 @@
         <v>7.4</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2">
+        <v>70</v>
+      </c>
+      <c r="H2">
         <v>1485</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>100</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>141.800003</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>74.199996999999996</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>600</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.08</v>
-      </c>
-      <c r="M2">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>80</v>
@@ -1233,28 +1234,28 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
         <v>800</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>100</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>80</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>40</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>600</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.05</v>
-      </c>
-      <c r="M3">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1274,36 +1275,36 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G4">
+        <v>55</v>
+      </c>
+      <c r="H4">
         <v>810</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>150</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>81</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>40.5</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>600</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.05</v>
-      </c>
-      <c r="M4">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
       </c>
       <c r="C5">
         <v>97.800003000000004</v>
@@ -1315,36 +1316,36 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
         <v>977.5</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>150</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>126.5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>46</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>580</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.05</v>
-      </c>
-      <c r="M5">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1356,36 +1357,36 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6">
         <v>1000</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>50</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>600</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.05</v>
-      </c>
-      <c r="M6">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <v>114.800003</v>
@@ -1397,36 +1398,36 @@
         <v>5.4</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G7">
+        <v>70</v>
+      </c>
+      <c r="H7">
         <v>1147.5</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>100</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>155.199997</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>54</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>630</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.2</v>
-      </c>
-      <c r="M7">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>90</v>
@@ -1438,36 +1439,36 @@
         <v>4.5</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
         <v>900</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>150</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>45</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>600</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.05</v>
-      </c>
-      <c r="M8">
-        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1479,36 +1480,36 @@
         <v>5.2</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G9">
+        <v>50</v>
+      </c>
+      <c r="H9">
         <v>1000</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>100</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>68</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>52</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>550</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.05</v>
-      </c>
-      <c r="M9">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10">
         <v>97.800003000000004</v>
@@ -1520,36 +1521,36 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G10">
+        <v>65</v>
+      </c>
+      <c r="H10">
         <v>977.5</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>150</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>126.5</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>46</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>580</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.05</v>
-      </c>
-      <c r="M10">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>68</v>
@@ -1561,33 +1562,33 @@
         <v>3.2</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G11">
+        <v>50</v>
+      </c>
+      <c r="H11">
         <v>680</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>100</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>92</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>32</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>630</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.15</v>
-      </c>
-      <c r="M11">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1602,36 +1603,36 @@
         <v>4.5</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G12">
+        <v>55</v>
+      </c>
+      <c r="H12">
         <v>900</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>100</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>90</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>45</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>600</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.05</v>
-      </c>
-      <c r="M12">
-        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>97.800003000000004</v>
@@ -1643,33 +1644,33 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G13">
+        <v>65</v>
+      </c>
+      <c r="H13">
         <v>977.5</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>100</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>132.199997</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>46</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>630</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.2</v>
-      </c>
-      <c r="M13">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -1684,33 +1685,33 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="H14">
         <v>810</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>150</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>81</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>40.5</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>600</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.05</v>
-      </c>
-      <c r="M14">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
@@ -1725,36 +1726,36 @@
         <v>4.5</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G15">
+        <v>55</v>
+      </c>
+      <c r="H15">
         <v>900</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>100</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>90</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>45</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>600</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.05</v>
-      </c>
-      <c r="M15">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>168.800003</v>
@@ -1766,33 +1767,33 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G16">
+        <v>70</v>
+      </c>
+      <c r="H16">
         <v>1687.5</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>100</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>114.800003</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>87.800003000000004</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>550</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.05</v>
-      </c>
-      <c r="M16">
-        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>19</v>
@@ -1807,36 +1808,36 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G17">
+        <v>55</v>
+      </c>
+      <c r="H17">
         <v>810</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>150</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>76.5</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>40.5</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>600</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.05</v>
-      </c>
-      <c r="M17">
-        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>126.5</v>
@@ -1848,36 +1849,36 @@
         <v>6.3</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G18">
+        <v>65</v>
+      </c>
+      <c r="H18">
         <v>1265</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>100</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>120.699997</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>63.200001</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>600</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.08</v>
-      </c>
-      <c r="M18">
-        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>125</v>
@@ -1889,36 +1890,36 @@
         <v>6.5</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19">
         <v>1250</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>100</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>85</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>65</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>550</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.05</v>
-      </c>
-      <c r="M19">
-        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20">
         <v>68</v>
@@ -1930,36 +1931,36 @@
         <v>3.2</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20">
         <v>680</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>100</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>92</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>32</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>630</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.15</v>
-      </c>
-      <c r="M20">
-        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>109.199997</v>
@@ -1971,36 +1972,36 @@
         <v>5.8</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G21">
+        <v>65</v>
+      </c>
+      <c r="H21">
         <v>1092.5</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>120</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>109.199997</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>57.5</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>590</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.08</v>
-      </c>
-      <c r="M21">
-        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22">
         <v>90</v>
@@ -2012,36 +2013,36 @@
         <v>4.5</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G22">
+        <v>60</v>
+      </c>
+      <c r="H22">
         <v>900</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>150</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>90</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>45</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>600</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.05</v>
-      </c>
-      <c r="M22">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>85</v>
@@ -2053,36 +2054,36 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23">
         <v>60</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>850</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>150</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>110</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>40</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>580</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.05</v>
-      </c>
-      <c r="M23">
-        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24">
         <v>85</v>
@@ -2094,33 +2095,32 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24">
         <v>850</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>150</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>110</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>40</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>580</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>0.05</v>
-      </c>
-      <c r="M24">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterStats_Master.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="9420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22065" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterStats" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
   <si>
     <t>---</t>
   </si>
@@ -39,6 +39,9 @@
     <t>UltimateActionHandle</t>
   </si>
   <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
     <t>SummonCost</t>
   </si>
   <si>
@@ -75,142 +78,211 @@
     <t>Cost_Common</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Army_Ult")</t>
+  </si>
+  <si>
     <t>Char_Bard</t>
   </si>
   <si>
     <t>Cost_Uncommon</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Bard_Ult")</t>
+  </si>
+  <si>
     <t>Char_Binder</t>
   </si>
   <si>
     <t>Cost_Epic</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Binder_Ult")</t>
+  </si>
+  <si>
     <t>Char_Courier</t>
   </si>
   <si>
     <t>Cost_Rare</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Courier_Ult")</t>
+  </si>
+  <si>
     <t>Char_Demonia</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Demonia_Ult")</t>
+  </si>
+  <si>
     <t>Char_Enchanter</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Enchanter_Ult")</t>
+  </si>
+  <si>
     <t>Char_Guard</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Guard_Ult")</t>
+  </si>
+  <si>
     <t>Char_Hermit</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hermit_Ult")</t>
+  </si>
+  <si>
     <t>Char_Hornet</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hornet_Ult")</t>
+  </si>
+  <si>
     <t>Char_Looter</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Looter_Ult")</t>
+  </si>
+  <si>
     <t>Char_Maid</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Maid_Ult")</t>
+  </si>
+  <si>
     <t>Char_Merry</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Merry_Ult")</t>
+  </si>
+  <si>
     <t>Char_Muzzle</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Muzzle_Ult")</t>
+  </si>
+  <si>
     <t>Char_Noble</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Noble_Ult")</t>
+  </si>
+  <si>
     <t>Char_Nurse</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Nurse_Ult")</t>
+  </si>
+  <si>
     <t>Char_Outsider</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Outsider_Ult")</t>
+  </si>
+  <si>
     <t>Char_Pioneer</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Pioneer_Ult")</t>
+  </si>
+  <si>
     <t>Char_Rogue</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Rogue_Ult")</t>
+  </si>
+  <si>
     <t>Char_Tinker</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tinker_Ult")</t>
+  </si>
+  <si>
     <t>Char_Tuner</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tuner_Ult")</t>
+  </si>
+  <si>
     <t>Char_Weaver</t>
   </si>
   <si>
+    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Weaver_Ult")</t>
+  </si>
+  <si>
     <t>Char_Writer</t>
   </si>
   <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Army_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Bard_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Binder_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Courier_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Demonia_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Enchanter_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Guard_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hermit_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Hornet_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Looter_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Maid_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Merry_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Muzzle_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Noble_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Nurse_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Outsider_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Pioneer_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Rogue_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tinker_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Tuner_Ult")</t>
-  </si>
-  <si>
-    <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Weaver_Ult")</t>
-  </si>
-  <si>
     <t>(DataTable="/Script/Engine.DataTable'/Game/Data/Action/Ultimate/DT_UltimateStats.DT_UltimateStats'",RowName="Writer_Ult")</t>
+  </si>
+  <si>
+    <t>아누비스</t>
+  </si>
+  <si>
+    <t>아미</t>
+  </si>
+  <si>
+    <t>바드</t>
+  </si>
+  <si>
+    <t>바인더</t>
+  </si>
+  <si>
+    <t>쿠리어</t>
+  </si>
+  <si>
+    <t>데모니아</t>
+  </si>
+  <si>
+    <t>인챈터</t>
+  </si>
+  <si>
+    <t>가드</t>
+  </si>
+  <si>
+    <t>허밋</t>
+  </si>
+  <si>
+    <t>호넷</t>
+  </si>
+  <si>
+    <t>루터</t>
+  </si>
+  <si>
+    <t>메이드</t>
+  </si>
+  <si>
+    <t>메리</t>
+  </si>
+  <si>
+    <t>머즐</t>
+  </si>
+  <si>
+    <t>노블</t>
+  </si>
+  <si>
+    <t>너스</t>
+  </si>
+  <si>
+    <t>아웃사이더</t>
+  </si>
+  <si>
+    <t>파이오니어</t>
+  </si>
+  <si>
+    <t>로그</t>
+  </si>
+  <si>
+    <t>팅커</t>
+  </si>
+  <si>
+    <t>튜너</t>
+  </si>
+  <si>
+    <t>위버</t>
+  </si>
+  <si>
+    <t>라이터</t>
   </si>
 </sst>
 </file>
@@ -1128,14 +1200,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="6" max="6" width="51.125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1175,13 +1243,16 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>148.5</v>
@@ -1193,36 +1264,39 @@
         <v>7.4</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2">
         <v>70</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1485</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>100</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>141.800003</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>74.199996999999996</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>600</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>80</v>
@@ -1234,36 +1308,39 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3">
         <v>50</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>800</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>100</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>80</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>40</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>600</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>81</v>
@@ -1275,36 +1352,39 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4">
         <v>55</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>810</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>150</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>81</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>40.5</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>600</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>97.800003000000004</v>
@@ -1316,36 +1396,39 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5">
         <v>65</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>977.5</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>150</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>126.5</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>46</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>580</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -1357,36 +1440,39 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6">
         <v>60</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>1000</v>
-      </c>
-      <c r="I6">
-        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>50</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>600</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>114.800003</v>
@@ -1398,36 +1484,39 @@
         <v>5.4</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
         <v>70</v>
       </c>
       <c r="H7">
+        <v>70</v>
+      </c>
+      <c r="I7">
         <v>1147.5</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>100</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>155.199997</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>54</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>630</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>90</v>
@@ -1439,36 +1528,39 @@
         <v>4.5</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8">
         <v>60</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>900</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>150</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>90</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>45</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>600</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -1480,36 +1572,39 @@
         <v>5.2</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9">
         <v>50</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1000</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>100</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>68</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>52</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>550</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>97.800003000000004</v>
@@ -1521,36 +1616,39 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10">
         <v>65</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>977.5</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>150</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>126.5</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>46</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>580</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>68</v>
@@ -1562,36 +1660,39 @@
         <v>3.2</v>
       </c>
       <c r="F11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11">
         <v>50</v>
       </c>
-      <c r="G11">
-        <v>50</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>680</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>100</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>92</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>32</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>630</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -1603,36 +1704,39 @@
         <v>4.5</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12">
         <v>55</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>900</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>100</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>90</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>45</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>600</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>97.800003000000004</v>
@@ -1644,36 +1748,39 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13">
         <v>65</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>977.5</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>100</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>132.199997</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>46</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>630</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>81</v>
@@ -1685,36 +1792,39 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14">
         <v>55</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>810</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>150</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>81</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>40.5</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>600</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -1726,36 +1836,39 @@
         <v>4.5</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15">
         <v>55</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>900</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>100</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>90</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>45</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>600</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>168.800003</v>
@@ -1767,36 +1880,39 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16">
         <v>70</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1687.5</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>100</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>114.800003</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>87.800003000000004</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>550</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C17">
         <v>81</v>
@@ -1808,36 +1924,39 @@
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17">
         <v>55</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>810</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>150</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>76.5</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>40.5</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>600</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>126.5</v>
@@ -1849,36 +1968,39 @@
         <v>6.3</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
+        <v>52</v>
+      </c>
+      <c r="G18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18">
         <v>65</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>1265</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>100</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>120.699997</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>63.200001</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>600</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>125</v>
@@ -1890,36 +2012,39 @@
         <v>6.5</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19">
         <v>60</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>1250</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>100</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>85</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>65</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>550</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20">
         <v>68</v>
@@ -1931,36 +2056,39 @@
         <v>3.2</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20">
         <v>50</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>680</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>100</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>92</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>32</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>630</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>109.199997</v>
@@ -1972,36 +2100,39 @@
         <v>5.8</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
+        <v>58</v>
+      </c>
+      <c r="G21" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21">
         <v>65</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>1092.5</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>120</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>109.199997</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>57.5</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>590</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>90</v>
@@ -2013,36 +2144,39 @@
         <v>4.5</v>
       </c>
       <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22">
+        <v>60</v>
+      </c>
+      <c r="I22">
+        <v>900</v>
+      </c>
+      <c r="J22">
+        <v>150</v>
+      </c>
+      <c r="K22">
+        <v>90</v>
+      </c>
+      <c r="L22">
+        <v>45</v>
+      </c>
+      <c r="M22">
+        <v>600</v>
+      </c>
+      <c r="N22">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>61</v>
       </c>
-      <c r="G22">
-        <v>60</v>
-      </c>
-      <c r="H22">
-        <v>900</v>
-      </c>
-      <c r="I22">
-        <v>150</v>
-      </c>
-      <c r="J22">
-        <v>90</v>
-      </c>
-      <c r="K22">
-        <v>45</v>
-      </c>
-      <c r="L22">
-        <v>600</v>
-      </c>
-      <c r="M22">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>40</v>
-      </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C23">
         <v>85</v>
@@ -2056,34 +2190,37 @@
       <c r="F23" t="s">
         <v>62</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23">
         <v>60</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>850</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>150</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>110</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>40</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>580</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C24">
         <v>85</v>
@@ -2095,27 +2232,30 @@
         <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24">
+        <v>64</v>
+      </c>
+      <c r="G24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24">
         <v>60</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>850</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>150</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>110</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>40</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>580</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>0.05</v>
       </c>
     </row>

--- a/DesignData/Excel_Masters/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/CharacterStats_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
   <si>
     <t>---</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>라이터</t>
+  </si>
+  <si>
+    <t>BaseHealthRegen</t>
+  </si>
+  <si>
+    <t>BaseManaRegen</t>
   </si>
 </sst>
 </file>
@@ -1200,10 +1206,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1220,34 +1226,40 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1263,35 +1275,41 @@
       <c r="E2">
         <v>7.4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>65</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>70</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <v>1485</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>100</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>141.800003</v>
       </c>
-      <c r="L2">
+      <c r="N2">
         <v>74.199996999999996</v>
       </c>
-      <c r="M2">
+      <c r="O2">
         <v>600</v>
       </c>
-      <c r="N2">
+      <c r="P2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1307,35 +1325,41 @@
       <c r="E3">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>66</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>50</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>800</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>100</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>80</v>
       </c>
-      <c r="L3">
+      <c r="N3">
         <v>40</v>
       </c>
-      <c r="M3">
+      <c r="O3">
         <v>600</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1351,35 +1375,41 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>67</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>55</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <v>810</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <v>150</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <v>81</v>
       </c>
-      <c r="L4">
+      <c r="N4">
         <v>40.5</v>
       </c>
-      <c r="M4">
+      <c r="O4">
         <v>600</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1395,35 +1425,41 @@
       <c r="E5">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>68</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>65</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <v>977.5</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>150</v>
       </c>
-      <c r="K5">
+      <c r="M5">
         <v>126.5</v>
       </c>
-      <c r="L5">
+      <c r="N5">
         <v>46</v>
       </c>
-      <c r="M5">
+      <c r="O5">
         <v>580</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1439,35 +1475,41 @@
       <c r="E6">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>69</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>60</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <v>1000</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>100</v>
       </c>
-      <c r="K6">
+      <c r="M6">
         <v>100</v>
       </c>
-      <c r="L6">
+      <c r="N6">
         <v>50</v>
       </c>
-      <c r="M6">
+      <c r="O6">
         <v>600</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1483,35 +1525,41 @@
       <c r="E7">
         <v>5.4</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
         <v>30</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>70</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>70</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <v>1147.5</v>
       </c>
-      <c r="J7">
+      <c r="L7">
         <v>100</v>
       </c>
-      <c r="K7">
+      <c r="M7">
         <v>155.199997</v>
       </c>
-      <c r="L7">
+      <c r="N7">
         <v>54</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>630</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1527,35 +1575,41 @@
       <c r="E8">
         <v>4.5</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>71</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>60</v>
       </c>
-      <c r="I8">
+      <c r="K8">
         <v>900</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>150</v>
       </c>
-      <c r="K8">
+      <c r="M8">
         <v>90</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>45</v>
       </c>
-      <c r="M8">
+      <c r="O8">
         <v>600</v>
       </c>
-      <c r="N8">
+      <c r="P8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1571,35 +1625,41 @@
       <c r="E9">
         <v>5.2</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
         <v>34</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>72</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>50</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>1000</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>100</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <v>68</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>52</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>550</v>
       </c>
-      <c r="N9">
+      <c r="P9">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1615,35 +1675,41 @@
       <c r="E10">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>73</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>65</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>977.5</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>150</v>
       </c>
-      <c r="K10">
+      <c r="M10">
         <v>126.5</v>
       </c>
-      <c r="L10">
+      <c r="N10">
         <v>46</v>
       </c>
-      <c r="M10">
+      <c r="O10">
         <v>580</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1659,35 +1725,41 @@
       <c r="E11">
         <v>3.2</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>74</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>50</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>680</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>100</v>
       </c>
-      <c r="K11">
+      <c r="M11">
         <v>92</v>
       </c>
-      <c r="L11">
+      <c r="N11">
         <v>32</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>630</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1703,35 +1775,41 @@
       <c r="E12">
         <v>4.5</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
         <v>40</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>75</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>55</v>
       </c>
-      <c r="I12">
+      <c r="K12">
         <v>900</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>100</v>
       </c>
-      <c r="K12">
+      <c r="M12">
         <v>90</v>
       </c>
-      <c r="L12">
+      <c r="N12">
         <v>45</v>
       </c>
-      <c r="M12">
+      <c r="O12">
         <v>600</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1747,35 +1825,41 @@
       <c r="E13">
         <v>4.5999999999999996</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
         <v>42</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>76</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>65</v>
       </c>
-      <c r="I13">
+      <c r="K13">
         <v>977.5</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>100</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <v>132.199997</v>
       </c>
-      <c r="L13">
+      <c r="N13">
         <v>46</v>
       </c>
-      <c r="M13">
+      <c r="O13">
         <v>630</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1791,35 +1875,41 @@
       <c r="E14">
         <v>4</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
         <v>44</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>77</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>55</v>
       </c>
-      <c r="I14">
+      <c r="K14">
         <v>810</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>150</v>
       </c>
-      <c r="K14">
+      <c r="M14">
         <v>81</v>
       </c>
-      <c r="L14">
+      <c r="N14">
         <v>40.5</v>
       </c>
-      <c r="M14">
+      <c r="O14">
         <v>600</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -1835,35 +1925,41 @@
       <c r="E15">
         <v>4.5</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
         <v>46</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>78</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>55</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>900</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>100</v>
       </c>
-      <c r="K15">
+      <c r="M15">
         <v>90</v>
       </c>
-      <c r="L15">
+      <c r="N15">
         <v>45</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>600</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1879,35 +1975,41 @@
       <c r="E16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
         <v>48</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>79</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>70</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>1687.5</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>100</v>
       </c>
-      <c r="K16">
+      <c r="M16">
         <v>114.800003</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>87.800003000000004</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>550</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1923,35 +2025,41 @@
       <c r="E17">
         <v>4</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
         <v>50</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>80</v>
       </c>
-      <c r="H17">
+      <c r="J17">
         <v>55</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>810</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>150</v>
       </c>
-      <c r="K17">
+      <c r="M17">
         <v>76.5</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>40.5</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>600</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1967,35 +2075,41 @@
       <c r="E18">
         <v>6.3</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
         <v>52</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>81</v>
       </c>
-      <c r="H18">
+      <c r="J18">
         <v>65</v>
       </c>
-      <c r="I18">
+      <c r="K18">
         <v>1265</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>100</v>
       </c>
-      <c r="K18">
+      <c r="M18">
         <v>120.699997</v>
       </c>
-      <c r="L18">
+      <c r="N18">
         <v>63.200001</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>600</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -2011,35 +2125,41 @@
       <c r="E19">
         <v>6.5</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
         <v>54</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>82</v>
       </c>
-      <c r="H19">
+      <c r="J19">
         <v>60</v>
       </c>
-      <c r="I19">
+      <c r="K19">
         <v>1250</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>100</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>85</v>
       </c>
-      <c r="L19">
+      <c r="N19">
         <v>65</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>550</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2055,35 +2175,41 @@
       <c r="E20">
         <v>3.2</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
         <v>56</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>83</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>50</v>
       </c>
-      <c r="I20">
+      <c r="K20">
         <v>680</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>100</v>
       </c>
-      <c r="K20">
+      <c r="M20">
         <v>92</v>
       </c>
-      <c r="L20">
+      <c r="N20">
         <v>32</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>630</v>
       </c>
-      <c r="N20">
+      <c r="P20">
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -2099,35 +2225,41 @@
       <c r="E21">
         <v>5.8</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
         <v>58</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>84</v>
       </c>
-      <c r="H21">
+      <c r="J21">
         <v>65</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>1092.5</v>
       </c>
-      <c r="J21">
+      <c r="L21">
         <v>120</v>
       </c>
-      <c r="K21">
+      <c r="M21">
         <v>109.199997</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>57.5</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>590</v>
       </c>
-      <c r="N21">
+      <c r="P21">
         <v>0.08</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -2143,35 +2275,41 @@
       <c r="E22">
         <v>4.5</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
         <v>60</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>85</v>
       </c>
-      <c r="H22">
+      <c r="J22">
         <v>60</v>
       </c>
-      <c r="I22">
+      <c r="K22">
         <v>900</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>150</v>
       </c>
-      <c r="K22">
+      <c r="M22">
         <v>90</v>
       </c>
-      <c r="L22">
+      <c r="N22">
         <v>45</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>600</v>
       </c>
-      <c r="N22">
+      <c r="P22">
         <v>0.05</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -2187,35 +2325,41 @@
       <c r="E23">
         <v>4</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
         <v>62</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" t="s">
         <v>86</v>
       </c>
-      <c r="H23">
+      <c r="J23">
         <v>60</v>
       </c>
-      <c r="I23">
+      <c r="K23">
         <v>850</v>
       </c>
-      <c r="J23">
+      <c r="L23">
         <v>150</v>
       </c>
-      <c r="K23">
+      <c r="M23">
         <v>110</v>
       </c>
-      <c r="L23">
+      <c r="N23">
         <v>40</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>580</v>
       </c>
-      <c r="N23">
+      <c r="P23">
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -2231,31 +2375,37 @@
       <c r="E24">
         <v>4</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
         <v>64</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>87</v>
       </c>
-      <c r="H24">
+      <c r="J24">
         <v>60</v>
       </c>
-      <c r="I24">
+      <c r="K24">
         <v>850</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>150</v>
       </c>
-      <c r="K24">
+      <c r="M24">
         <v>110</v>
       </c>
-      <c r="L24">
+      <c r="N24">
         <v>40</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>580</v>
       </c>
-      <c r="N24">
+      <c r="P24">
         <v>0.05</v>
       </c>
     </row>
